--- a/files/九龙-何文田-瑜一第IC期.xlsx
+++ b/files/九龙-何文田-瑜一第IC期.xlsx
@@ -905,7 +905,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14186,7 +14186,7 @@
           <t>B | 1208呎 (4+房)
 $4828万
 $39,967/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -14202,7 +14202,7 @@
           <t>A | 934呎 (3房)
 $2989万
 $32,000/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -14210,7 +14210,7 @@
           <t>B | 576呎 (2房)
 $1603万
 $27,833/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -14218,7 +14218,7 @@
           <t>C | 904呎 (3房)
 $3030万
 $33,522/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14233,7 @@
           <t>A | 934呎 (3房)
 $3022万
 $32,353/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -14241,7 +14241,7 @@
           <t>B | 576呎 (2房)
 $1875万
 $32,554/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -14249,7 +14249,7 @@
           <t>C | 904呎 (3房)
 $2971万
 $32,866/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14264,7 @@
           <t>A | 934呎 (3房)
 $2861万
 $30,635/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -14272,7 +14272,7 @@
           <t>B | 576呎 (2房)
 $1845万
 $32,039/呎
-(23年-06月-08日)</t>
+(23年-06月-09日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -14280,7 +14280,7 @@
           <t>C | 904呎 (3房)
 $2913万
 $32,221/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
           <t>A | 934呎 (3房)
 $2904万
 $31,096/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -14303,7 +14303,7 @@
           <t>B | 576呎 (2房)
 $1765万
 $30,634/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -14311,7 +14311,7 @@
           <t>C | 904呎 (3房)
 $2856万
 $31,588/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14326,7 @@
           <t>A | 934呎 (3房)
 $2849万
 $30,500/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -14334,7 +14334,7 @@
           <t>B | 576呎 (2房)
 $1806万
 $31,362/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -14342,7 +14342,7 @@
           <t>C | 904呎 (3房)
 $2833万
 $31,337/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
           <t>A | 934呎 (3房)
 $2858万
 $30,605/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -14365,7 +14365,7 @@
           <t>B | 576呎 (2房)
 $1783万
 $30,954/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -14373,7 +14373,7 @@
           <t>C | 904呎 (3房)
 $2712万
 $30,000/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -14388,7 +14388,7 @@
           <t>A | 934呎 (3房)
 $2836万
 $30,361/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -14396,7 +14396,7 @@
           <t>B | 576呎 (2房)
 $1755万
 $30,474/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -14404,7 +14404,7 @@
           <t>C | 904呎 (3房)
 $2763万
 $30,569/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
           <t>A | 934呎 (3房)
 $2836万
 $30,361/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -14427,7 +14427,7 @@
           <t>B | 576呎 (2房)
 $1755万
 $30,474/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -14435,7 +14435,7 @@
           <t>C | 904呎 (3房)
 $2716万
 $30,048/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
           <t>A | 934呎 (3房)
 $2801万
 $29,986/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -14458,7 +14458,7 @@
           <t>B | 576呎 (2房)
 $1698万
 $29,472/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -14466,7 +14466,7 @@
           <t>C | 904呎 (3房)
 $2558万
 $28,300/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
           <t>A | 934呎 (3房)
 $2597万
 $27,800/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -14489,7 +14489,7 @@
           <t>B | 576呎 (2房)
 $1649万
 $28,634/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -14497,7 +14497,7 @@
           <t>C | 904呎 (3房)
 $2590万
 $28,656/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14512,7 +14512,7 @@
           <t>A | 934呎 (3房)
 $2756万
 $29,504/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -14520,7 +14520,7 @@
           <t>B | 576呎 (2房)
 $1676万
 $29,095/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -14528,7 +14528,7 @@
           <t>C | 904呎 (3房)
 $2584万
 $28,589/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
           <t>A | 934呎 (3房)
 $2729万
 $29,214/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -14551,7 +14551,7 @@
           <t>B | 576呎 (2房)
 $1647万
 $28,595/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -14559,7 +14559,7 @@
           <t>C | 904呎 (3房)
 $2581万
 $28,554/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
           <t>A | 934呎 (3房)
 $2676万
 $28,646/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -14582,7 +14582,7 @@
           <t>B | 576呎 (2房)
 $1595万
 $27,697/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -14590,7 +14590,7 @@
           <t>C | 904呎 (3房)
 $2499万
 $27,644/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
           <t>A | 934呎 (3房)
 $2620万
 $28,050/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -14613,7 +14613,7 @@
           <t>B | 576呎 (2房)
 $1549万
 $26,892/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -14621,7 +14621,7 @@
           <t>C | 904呎 (3房)
 $2426万
 $26,838/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14636,7 @@
           <t>A | 934呎 (3房)
 $2569万
 $27,500/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -14644,7 +14644,7 @@
           <t>B | 576呎 (2房)
 $1519万
 $26,365/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -14652,7 +14652,7 @@
           <t>C | 904呎 (3房)
 $2338万
 $25,864/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14667,7 +14667,7 @@
           <t>A | 934呎 (3房)
 $2518万
 $26,961/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -14675,7 +14675,7 @@
           <t>B | 576呎 (2房)
 $1489万
 $25,847/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -14683,7 +14683,7 @@
           <t>C | 904呎 (3房)
 $2332万
 $25,796/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
           <t>A | 934呎 (3房)
 $2385万
 $25,531/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -14706,7 +14706,7 @@
           <t>B | 576呎 (2房)
 $1325万
 $23,007/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -14714,7 +14714,7 @@
           <t>C | 904呎 (3房)
 $2286万
 $25,290/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
           <t>A | 934呎 (3房)
 $2279万
 $24,400/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -14737,7 +14737,7 @@
           <t>B | 576呎 (2房)
 $1407万
 $24,421/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -14745,7 +14745,7 @@
           <t>C | 904呎 (3房)
 $2203万
 $24,372/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
           <t>A | 934呎 (3房)
 $2310万
 $24,731/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -14768,7 +14768,7 @@
           <t>B | 576呎 (2房)
 $1399万
 $24,282/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -14776,7 +14776,7 @@
           <t>C | 904呎 (3房)
 $2139万
 $23,662/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
           <t>A | 934呎 (3房)
 $2299万
 $24,611/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -14799,7 +14799,7 @@
           <t>B | 576呎 (2房)
 $1338万
 $23,223/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -14807,7 +14807,7 @@
           <t>C | 904呎 (3房)
 $2113万
 $23,372/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14822,7 +14822,7 @@
           <t>A | 934呎 (3房)
 $2174万
 $23,274/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -14830,7 +14830,7 @@
           <t>B | 576呎 (2房)
 $1372万
 $23,812/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -14838,7 +14838,7 @@
           <t>C | 904呎 (3房)
 $2045万
 $22,621/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -14853,7 +14853,7 @@
           <t>A | 891呎 (3房)
 $2617万
 $29,374/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -14861,7 +14861,7 @@
           <t>B | 533呎 (2房)
 $1538万
 $28,855/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -14869,7 +14869,7 @@
           <t>C | 861呎 (3房)
 $2435万
 $28,280/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -15019,7 +15019,7 @@
           <t>A | 656呎 (3房)
 $2377万
 $36,240/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -15027,7 +15027,7 @@
           <t>B | 461呎 (2房)
 $1620万
 $35,146/呎
-(23年-05月-03日)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -15035,7 +15035,7 @@
           <t>C | 465呎 (2房)
 $1395万
 $29,998/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -15043,7 +15043,7 @@
           <t>D | 466呎 (2房)
 $1631万
 $34,992/呎
-(23年-05月-31日)</t>
+(23年-06月-01日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -15051,7 +15051,7 @@
           <t>E | 518呎 (2房)
 $1792万
 $34,598/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -15059,7 +15059,7 @@
           <t>F | 521呎 (2房)
 $1497万
 $28,738/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
           <t>A | 656呎 (3房)
 $2149万
 $32,755/呎
-(24年-03月-12日)</t>
+(24年-03月-13日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -15082,7 +15082,7 @@
           <t>B | 461呎 (2房)
 $1275万
 $27,655/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -15090,7 +15090,7 @@
           <t>C | 465呎 (2房)
 $1421万
 $30,563/呎
-(23年-07月-18日)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -15098,7 +15098,7 @@
           <t>D | 466呎 (2房)
 $1273万
 $27,317/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -15106,7 +15106,7 @@
           <t>E | 518呎 (2房)
 $1648万
 $31,811/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -15114,7 +15114,7 @@
           <t>F | 521呎 (2房)
 $1375万
 $26,397/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -15129,7 +15129,7 @@
           <t>A | 656呎 (3房)
 $2166万
 $33,021/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -15137,7 +15137,7 @@
           <t>B | 461呎 (2房)
 $1300万
 $28,208/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -15145,7 +15145,7 @@
           <t>C | 465呎 (2房)
 $1260万
 $27,101/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -15153,7 +15153,7 @@
           <t>D | 466呎 (2房)
 $1254万
 $26,912/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -15161,7 +15161,7 @@
           <t>E | 518呎 (2房)
 $1623万
 $31,340/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -15169,7 +15169,7 @@
           <t>F | 521呎 (2房)
 $1355万
 $26,001/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
           <t>A | 656呎 (3房)
 $1814万
 $27,654/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -15192,7 +15192,7 @@
           <t>B | 461呎 (2房)
 $1238万
 $26,844/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -15200,7 +15200,7 @@
           <t>C | 465呎 (2房)
 $1363万
 $29,315/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -15208,7 +15208,7 @@
           <t>D | 466呎 (2房)
 $1445万
 $31,015/呎
-(23年-06月-07日)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -15216,7 +15216,7 @@
           <t>E | 518呎 (2房)
 $1599万
 $30,876/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -15224,7 +15224,7 @@
           <t>F | 521呎 (2房)
 $1335万
 $25,617/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
           <t>A | 656呎 (3房)
 $2103万
 $32,053/呎
-(23年-06月-19日)</t>
+(23年-06月-20日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -15247,7 +15247,7 @@
           <t>B | 461呎 (2房)
 $1262万
 $27,381/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -15255,7 +15255,7 @@
           <t>C | 465呎 (2房)
 $1359万
 $29,227/呎
-(23年-07月-24日)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -15263,7 +15263,7 @@
           <t>D | 466呎 (2房)
 $1375万
 $29,517/呎
-(23年-06月-01日)</t>
+(23年-06月-02日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -15271,7 +15271,7 @@
           <t>E | 518呎 (2房)
 $1454万
 $28,065/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -15279,7 +15279,7 @@
           <t>F | 521呎 (2房)
 $1321万
 $25,355/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
           <t>A | 656呎 (3房)
 $2071万
 $31,570/呎
-(23年-07月-11日)</t>
+(23年-07月-12日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -15302,7 +15302,7 @@
           <t>B | 461呎 (2房)
 $1201万
 $26,055/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -15310,7 +15310,7 @@
           <t>C | 465呎 (2房)
 $1339万
 $28,794/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -15318,7 +15318,7 @@
           <t>D | 466呎 (2房)
 $1403万
 $30,105/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -15326,7 +15326,7 @@
           <t>E | 518呎 (2房)
 $1545万
 $29,831/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -15334,7 +15334,7 @@
           <t>F | 521呎 (2房)
 $1312万
 $25,174/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15349,7 @@
           <t>A | 656呎 (3房)
 $1747万
 $26,631/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -15357,7 +15357,7 @@
           <t>B | 461呎 (2房)
 $1194万
 $25,900/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -15365,7 +15365,7 @@
           <t>C | 465呎 (2房)
 $1331万
 $28,622/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -15373,7 +15373,7 @@
           <t>D | 466呎 (2房)
 $1371万
 $29,417/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -15381,7 +15381,7 @@
           <t>E | 518呎 (2房)
 $1564万
 $30,200/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -15389,7 +15389,7 @@
           <t>F | 521呎 (2房)
 $1519万
 $29,146/呎
-(23年-06月-11日)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
           <t>A | 656呎 (3房)
 $1733万
 $26,421/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -15412,7 +15412,7 @@
           <t>B | 461呎 (2房)
 $1187万
 $25,747/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -15420,7 +15420,7 @@
           <t>C | 465呎 (2房)
 $1191万
 $25,608/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -15428,7 +15428,7 @@
           <t>D | 466呎 (2房)
 $1386万
 $29,748/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -15436,7 +15436,7 @@
           <t>E | 518呎 (2房)
 $1417万
 $27,362/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -15444,7 +15444,7 @@
           <t>F | 521呎 (2房)
 $1448万
 $27,784/呎
-(23年-05月-07日)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -15459,10 +15459,65 @@
           <t>A | 656呎 (3房)
 $2024万
 $30,850/呎
-(23年-05月-28日)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 461呎 (2房)
+$1181万
+$25,616/呎
+(25年-09月-03日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$1363万
+$29,311/呎
+(23年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 466呎 (2房)
+$1379万
+$29,601/呎
+(23年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 518呎 (2房)
+$1523万
+$29,408/呎
+(23年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 521呎 (2房)
+$1478万
+$28,369/呎
+(23年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 656呎 (3房)
+$1720万
+$26,223/呎
+(25年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 461呎 (2房)
 $1181万
@@ -15470,75 +15525,20 @@
 (25年-09月-02日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 465呎 (2房)
 $1363万
 $29,311/呎
-(23年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
+(23年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 466呎 (2房)
 $1379万
 $29,601/呎
-(23年-04月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>E | 518呎 (2房)
-$1523万
-$29,408/呎
-(23年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
-        <is>
-          <t>F | 521呎 (2房)
-$1478万
-$28,369/呎
-(23年-04月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 656呎 (3房)
-$1720万
-$26,223/呎
-(25年-09月-01日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 461呎 (2房)
-$1181万
-$25,616/呎
-(25年-09月-01日)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>C | 465呎 (2房)
-$1363万
-$29,311/呎
-(23年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>D | 466呎 (2房)
-$1379万
-$29,601/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -15546,7 +15546,7 @@
           <t>E | 518呎 (2房)
 $1478万
 $28,542/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -15554,7 +15554,7 @@
           <t>F | 521呎 (2房)
 $1457万
 $27,957/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -15569,7 +15569,7 @@
           <t>A | 656呎 (3房)
 $1994万
 $30,393/呎
-(23年-06月-28日)</t>
+(23年-06月-29日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -15577,7 +15577,7 @@
           <t>B | 461呎 (2房)
 $1349万
 $29,263/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -15585,7 +15585,7 @@
           <t>C | 465呎 (2房)
 $1343万
 $28,877/呎
-(23年-05月-29日)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -15593,7 +15593,7 @@
           <t>D | 466呎 (2房)
 $1359万
 $29,163/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -15601,7 +15601,7 @@
           <t>E | 518呎 (2房)
 $1484万
 $28,646/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -15609,7 +15609,7 @@
           <t>F | 521呎 (2房)
 $1440万
 $27,646/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
           <t>A | 656呎 (3房)
 $1973万
 $30,080/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -15632,7 +15632,7 @@
           <t>B | 461呎 (2房)
 $1281万
 $27,788/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -15640,7 +15640,7 @@
           <t>C | 465呎 (2房)
 $1148万
 $24,688/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -15648,7 +15648,7 @@
           <t>D | 466呎 (2房)
 $1334万
 $28,630/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -15656,7 +15656,7 @@
           <t>E | 518呎 (2房)
 $1449万
 $27,973/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -15664,7 +15664,7 @@
           <t>F | 521呎 (2房)
 $1408万
 $27,030/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
           <t>A | 656呎 (3房)
 $1650万
 $25,146/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -15687,7 +15687,7 @@
           <t>B | 461呎 (2房)
 $1321万
 $28,654/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -15695,7 +15695,7 @@
           <t>C | 465呎 (2房)
 $1293万
 $27,803/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -15703,7 +15703,7 @@
           <t>D | 466呎 (2房)
 $1329万
 $28,517/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -15711,7 +15711,7 @@
           <t>E | 518呎 (2房)
 $1443万
 $27,859/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -15719,7 +15719,7 @@
           <t>F | 521呎 (2房)
 $1404万
 $26,949/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
           <t>A | 656呎 (3房)
 $1641万
 $25,013/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -15742,7 +15742,7 @@
           <t>B | 461呎 (2房)
 $1316万
 $28,544/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -15750,7 +15750,7 @@
           <t>C | 465呎 (2房)
 $1310万
 $28,171/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -15758,7 +15758,7 @@
           <t>D | 466呎 (2房)
 $1324万
 $28,402/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -15766,7 +15766,7 @@
           <t>E | 518呎 (2房)
 $1437万
 $27,751/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -15774,7 +15774,7 @@
           <t>F | 521呎 (2房)
 $1400万
 $26,869/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -15789,7 +15789,7 @@
           <t>A | 656呎 (3房)
 $1876万
 $28,598/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -15797,7 +15797,7 @@
           <t>B | 461呎 (2房)
 $1266万
 $27,460/呎
-(23年-04月-01日)</t>
+(23年-04月-02日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -15805,7 +15805,7 @@
           <t>C | 465呎 (2房)
 $1305万
 $28,058/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -15813,7 +15813,7 @@
           <t>D | 466呎 (2房)
 $1318万
 $28,288/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -15821,7 +15821,7 @@
           <t>E | 518呎 (2房)
 $1383万
 $26,695/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -15829,7 +15829,7 @@
           <t>F | 521呎 (2房)
 $1374万
 $26,368/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15844,7 @@
           <t>A | 656呎 (3房)
 $1624万
 $24,751/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -15852,7 +15852,7 @@
           <t>B | 461呎 (2房)
 $1305万
 $28,316/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -15860,7 +15860,7 @@
           <t>C | 465呎 (2房)
 $1130万
 $24,297/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -15868,7 +15868,7 @@
           <t>D | 466呎 (2房)
 $1313万
 $28,177/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -15876,7 +15876,7 @@
           <t>E | 518呎 (2房)
 $1308万
 $25,260/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -15884,7 +15884,7 @@
           <t>F | 521呎 (2房)
 $1342万
 $25,766/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -15899,7 +15899,7 @@
           <t>A | 656呎 (3房)
 $1905万
 $29,041/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -15907,7 +15907,7 @@
           <t>B | 461呎 (2房)
 $1300万
 $28,202/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -15915,7 +15915,7 @@
           <t>C | 465呎 (2房)
 $1294万
 $27,834/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -15923,7 +15923,7 @@
           <t>D | 466呎 (2房)
 $1124万
 $24,126/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -15931,7 +15931,7 @@
           <t>E | 518呎 (2房)
 $1420万
 $27,419/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -15939,7 +15939,7 @@
           <t>F | 521呎 (2房)
 $1349万
 $25,890/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
           <t>A | 656呎 (3房)
 $1601万
 $24,405/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -15962,7 +15962,7 @@
           <t>B | 461呎 (2房)
 $1118万
 $24,244/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -15970,7 +15970,7 @@
           <t>C | 465呎 (2房)
 $1294万
 $27,834/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -15978,7 +15978,7 @@
           <t>D | 466呎 (2房)
 $1308万
 $28,064/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -15986,7 +15986,7 @@
           <t>E | 518呎 (2房)
 $1303万
 $25,162/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -15994,7 +15994,7 @@
           <t>F | 521呎 (2房)
 $1349万
 $25,890/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
           <t>A | 656呎 (3房)
 $1890万
 $28,811/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -16017,7 +16017,7 @@
           <t>B | 461呎 (2房)
 $1238万
 $26,857/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -16025,7 +16025,7 @@
           <t>C | 465呎 (2房)
 $1239万
 $26,639/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -16033,7 +16033,7 @@
           <t>D | 466呎 (2房)
 $1289万
 $27,661/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -16041,7 +16041,7 @@
           <t>E | 518呎 (2房)
 $1409万
 $27,202/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -16049,7 +16049,7 @@
           <t>F | 521呎 (2房)
 $1339万
 $25,709/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16064,7 @@
           <t>A | 656呎 (3房)
 $1882万
 $28,696/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -16072,7 +16072,7 @@
           <t>B | 461呎 (2房)
 $1277万
 $27,696/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -16080,7 +16080,7 @@
           <t>C | 465呎 (2房)
 $1274万
 $27,401/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -16088,7 +16088,7 @@
           <t>D | 466呎 (2房)
 $1104万
 $23,683/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -16096,7 +16096,7 @@
           <t>E | 518呎 (2房)
 $1403万
 $27,093/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -16104,7 +16104,7 @@
           <t>F | 521呎 (2房)
 $1327万
 $25,466/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -16119,7 +16119,7 @@
           <t>A | 656呎 (3房)
 $1576万
 $24,020/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -16127,7 +16127,7 @@
           <t>B | 461呎 (2房)
 $1228万
 $26,643/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -16135,7 +16135,7 @@
           <t>C | 465呎 (2房)
 $1269万
 $27,291/呎
-(23年-05月-02日)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -16143,7 +16143,7 @@
           <t>D | 466呎 (2房)
 $1279万
 $27,440/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -16151,7 +16151,7 @@
           <t>E | 518呎 (2房)
 $1398万
 $26,984/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -16159,7 +16159,7 @@
           <t>F | 521呎 (2房)
 $1308万
 $25,101/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
           <t>A | 656呎 (3房)
 $1868万
 $28,468/呎
-(23年-06月-04日)</t>
+(23年-06月-05日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -16182,7 +16182,7 @@
           <t>B | 461呎 (2房)
 $1089万
 $23,617/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -16190,7 +16190,7 @@
           <t>C | 465呎 (2房)
 $1264万
 $27,182/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -16198,7 +16198,7 @@
           <t>D | 466呎 (2房)
 $1274万
 $27,331/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -16206,7 +16206,7 @@
           <t>E | 518呎 (2房)
 $1369万
 $26,419/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -16214,7 +16214,7 @@
           <t>F | 521呎 (2房)
 $1297万
 $24,897/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
           <t>A | 656呎 (3房)
 $1860万
 $28,354/呎
-(23年-05月-03日)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -16237,7 +16237,7 @@
           <t>B | 461呎 (2房)
 $1261万
 $27,364/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -16245,7 +16245,7 @@
           <t>C | 465呎 (2房)
 $1259万
 $27,074/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -16253,7 +16253,7 @@
           <t>D | 466呎 (2房)
 $1269万
 $27,223/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -16261,7 +16261,7 @@
           <t>E | 518呎 (2房)
 $1387万
 $26,772/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -16269,7 +16269,7 @@
           <t>F | 521呎 (2房)
 $1284万
 $24,652/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
           <t>A | 619呎 (3房)
 $2022万
 $32,665/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -16292,7 +16292,7 @@
           <t>B | 423呎 (2房)
 $1132万
 $26,754/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -16300,7 +16300,7 @@
           <t>C | 427呎 (2房)
 $1309万
 $30,666/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -16308,7 +16308,7 @@
           <t>D | 428呎 (2房)
 $1317万
 $30,769/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -16316,7 +16316,7 @@
           <t>E | 481呎 (2房)
 $1503万
 $31,237/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -16324,7 +16324,7 @@
           <t>F | 483呎 (2房)
 $1496万
 $30,978/呎
-(23年-05月-02日)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
     </row>
